--- a/data-manipulation-scripts/sheets-cleanup/sheets/INTERRUPTOR PISCA - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/INTERRUPTOR PISCA - 02_02.xlsx
@@ -28,7 +28,7 @@
     <t>7898939000030</t>
   </si>
   <si>
-    <t>INTERRUPTOR PISCA BHD PHENIX</t>
+    <t>INTERRUPTOR PISCA BHD PHOENIX</t>
   </si>
   <si>
     <t>7893986585318</t>
@@ -340,7 +340,9 @@
       <c r="C2" s="2">
         <v>8.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -352,7 +354,9 @@
       <c r="C3" s="2">
         <v>5.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>10.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
